--- a/benchmarks/v8/results_v8.xlsx
+++ b/benchmarks/v8/results_v8.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -81,6 +86,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1437,14 +1445,32 @@
       <c r="C24" s="2" t="n">
         <v>149764</v>
       </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>916687730</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6120.88</v>
+      </c>
       <c r="F24" t="n">
         <v>138</v>
       </c>
+      <c r="G24" t="n">
+        <v>105729.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>766.16</v>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>149193399</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>precision: untimed reports 149,193,399 spurious violating endings, timed none; timed explores 6120.9x fewer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1501,14 +1527,32 @@
       <c r="C26" s="2" t="n">
         <v>3906252</v>
       </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>3348560324</v>
+      </c>
+      <c r="E26" t="n">
+        <v>857.23</v>
+      </c>
       <c r="F26" t="n">
         <v>973.5</v>
       </c>
+      <c r="G26" t="n">
+        <v>109144</v>
+      </c>
+      <c r="H26" t="n">
+        <v>112.12</v>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>57609804</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>precision: untimed reports 57,609,804 spurious violating endings, timed none; timed explores 857.2x fewer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4589,24 +4633,35 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="F33" s="2" t="n"/>
-      <c r="G33" s="3" t="n"/>
+      <c r="G33" s="3" t="n">
+        <v>141418.2</v>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J33" s="2" t="n"/>
-      <c r="K33" s="3" t="n"/>
+      <c r="K33" s="3" t="n">
+        <v>119253.7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.84</v>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>96300000 explored (397160 execs, 95902840 blocked); 636600000 explored (98154 execs, 636501846 blocked)</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>--clients 7 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -5427,11 +5482,18 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>97875995</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>107700.2</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>finished</t>
@@ -5443,13 +5505,22 @@
       <c r="K46" s="3" t="n">
         <v>14650.8</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46" s="5" t="n">
         <v>48006837</v>
       </c>
+      <c r="M46" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.14</v>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>1</t>
         </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
@@ -5481,11 +5552,18 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>296781933</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>91161.5</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>finished</t>
@@ -5497,13 +5575,22 @@
       <c r="K47" s="3" t="n">
         <v>11976.7</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47" s="5" t="n">
         <v>127970073</v>
       </c>
+      <c r="M47" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.13</v>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
@@ -5535,11 +5622,18 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>148678165</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>79486.3</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>finished</t>
@@ -5551,13 +5645,22 @@
       <c r="K48" s="3" t="n">
         <v>17477.7</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48" s="5" t="n">
         <v>94819803</v>
       </c>
+      <c r="M48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.22</v>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
@@ -5659,11 +5762,18 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>105986347</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>85294.2</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>finished</t>
@@ -5675,13 +5785,22 @@
       <c r="K50" s="3" t="n">
         <v>15773.5</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50" s="5" t="n">
         <v>74063943</v>
       </c>
+      <c r="M50" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.18</v>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
@@ -5713,11 +5832,18 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>98579689</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>89370.7</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>finished</t>
@@ -5729,13 +5855,22 @@
       <c r="K51" s="3" t="n">
         <v>15240.2</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51" s="5" t="n">
         <v>65803563</v>
       </c>
+      <c r="M51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.17</v>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>8</t>
         </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
@@ -5767,11 +5902,18 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>205078132</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>71241.60000000001</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>finished</t>
@@ -5783,13 +5925,22 @@
       <c r="K52" s="3" t="n">
         <v>13202.8</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52" s="5" t="n">
         <v>127970073</v>
       </c>
+      <c r="M52" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.19</v>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>8</t>
         </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
@@ -7708,24 +7859,35 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="F80" s="2" t="n"/>
-      <c r="G80" s="3" t="n"/>
+      <c r="G80" s="3" t="n">
+        <v>151797.1</v>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J80" s="2" t="n"/>
-      <c r="K80" s="3" t="n"/>
+      <c r="K80" s="3" t="n">
+        <v>151797.1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>113900000 explored (2188 execs, 113897812 blocked); 860600000 explored (78126 execs, 860521874 blocked)</t>
+        </is>
+      </c>
       <c r="R80" t="inlineStr">
         <is>
           <t>--mode timed --nodes 9 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -9366,16 +9528,29 @@
       <c r="G106" s="3" t="n">
         <v>723.2</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H106" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>4225182246</v>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>105398</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>1296170304</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1050.36</v>
+      </c>
+      <c r="N106" t="n">
+        <v>145.74</v>
+      </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>8</t>
@@ -9506,11 +9681,18 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="n"/>
-      <c r="G109" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>948746800</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>80357.89999999999</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
       <c r="J109" s="2" t="n"/>
       <c r="K109" s="3" t="n"/>
       <c r="O109" t="inlineStr">
@@ -9518,6 +9700,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
@@ -9588,11 +9773,18 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>726066844</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>94837.8</v>
+      </c>
+      <c r="H111" t="n">
+        <v>4242432</v>
+      </c>
       <c r="J111" s="2" t="n"/>
       <c r="K111" s="3" t="n"/>
       <c r="O111" t="inlineStr">
@@ -9600,6 +9792,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
@@ -9670,11 +9865,18 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="n"/>
-      <c r="G113" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>717027100</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>70528.10000000001</v>
+      </c>
+      <c r="H113" t="n">
+        <v>4242432</v>
+      </c>
       <c r="J113" s="2" t="n"/>
       <c r="K113" s="3" t="n"/>
       <c r="O113" t="inlineStr">
@@ -9682,6 +9884,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
@@ -9858,11 +10063,13 @@
       <c r="G117" s="3" t="n"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J117" s="2" t="n"/>
-      <c r="K117" s="3" t="n"/>
+      <c r="K117" s="3" t="n">
+        <v>93325.3</v>
+      </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>8</t>
@@ -9896,17 +10103,23 @@
       <c r="G118" s="3" t="n"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J118" s="2" t="n"/>
-      <c r="K118" s="3" t="n"/>
+      <c r="K118" s="3" t="n">
+        <v>93606.7</v>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>100000 explored (6113 execs, 93887 blocked)</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
@@ -10015,16 +10228,29 @@
       <c r="G120" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="H120" t="n">
+      <c r="H120" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="n"/>
-      <c r="K120" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>916687730</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>105729.8</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>149193399</v>
+      </c>
+      <c r="M120" t="n">
+        <v>6120.88</v>
+      </c>
+      <c r="N120" t="n">
+        <v>766.16</v>
+      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>1</t>
@@ -10801,12 +11027,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>253042724</v>
+      </c>
       <c r="G133" s="3" t="n">
-        <v>3634</v>
+        <v>99903.8</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
       </c>
       <c r="J133" s="2" t="n"/>
       <c r="K133" s="3" t="n"/>
@@ -10815,9 +11046,12 @@
           <t>6</t>
         </is>
       </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>error (exit -9)</t>
+          <t>rule A rerun</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11689,17 +11923,23 @@
       <c r="G147" s="3" t="n"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J147" s="2" t="n"/>
-      <c r="K147" s="3" t="n"/>
+      <c r="K147" s="3" t="n">
+        <v>147683.9</v>
+      </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>1885100000 explored (22973507 execs, 1862126493 blocked)</t>
+        </is>
+      </c>
       <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -11727,17 +11967,23 @@
       <c r="G148" s="3" t="n"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J148" s="2" t="n"/>
-      <c r="K148" s="3" t="n"/>
+      <c r="K148" s="3" t="n">
+        <v>147680.9</v>
+      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>1725800000 explored (3751296 execs, 1722048704 blocked)</t>
+        </is>
+      </c>
       <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
@@ -11772,16 +12018,29 @@
       <c r="G149" s="3" t="n">
         <v>973.5</v>
       </c>
-      <c r="H149" t="n">
+      <c r="H149" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n"/>
-      <c r="K149" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>3348560324</v>
+      </c>
+      <c r="K149" s="3" t="n">
+        <v>109144</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>57609804</v>
+      </c>
+      <c r="M149" t="n">
+        <v>857.23</v>
+      </c>
+      <c r="N149" t="n">
+        <v>112.12</v>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>4</t>
@@ -12423,16 +12682,29 @@
       <c r="G159" s="3" t="n">
         <v>130.3</v>
       </c>
-      <c r="H159" t="n">
+      <c r="H159" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n"/>
-      <c r="K159" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>2910916444</v>
+      </c>
+      <c r="K159" s="3" t="n">
+        <v>82439.7</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>99314832</v>
+      </c>
+      <c r="M159" t="n">
+        <v>8215.969999999999</v>
+      </c>
+      <c r="N159" t="n">
+        <v>632.6900000000001</v>
+      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>4</t>
@@ -13691,11 +13963,16 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J178" s="2" t="n"/>
-      <c r="K178" s="3" t="n"/>
+      <c r="K178" s="3" t="n">
+        <v>140675</v>
+      </c>
+      <c r="N178" t="n">
+        <v>202.44</v>
+      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>1</t>
@@ -13704,7 +13981,11 @@
       <c r="P178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>1335200000 explored (667600006 execs, 667599994 blocked)</t>
+        </is>
+      </c>
       <c r="R178" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 6 --retries 2 --w-ratio 3</t>
@@ -13870,11 +14151,24 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n"/>
-      <c r="K181" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>1001630912</v>
+      </c>
+      <c r="K181" s="3" t="n">
+        <v>92557.7</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>10268.71</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1039.97</v>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>1</t>
@@ -13927,11 +14221,16 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J182" s="2" t="n"/>
-      <c r="K182" s="3" t="n"/>
+      <c r="K182" s="3" t="n">
+        <v>140692.1</v>
+      </c>
+      <c r="N182" t="n">
+        <v>318.09</v>
+      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>1</t>
@@ -13940,7 +14239,11 @@
       <c r="P182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>1691300000 explored (845650064 execs, 845649936 blocked)</t>
+        </is>
+      </c>
       <c r="R182" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 2 --retries 7 --w-ratio 3</t>
@@ -15837,11 +16140,13 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="F214" s="2" t="n"/>
-      <c r="G214" s="3" t="n"/>
+      <c r="G214" s="3" t="n">
+        <v>93493.8</v>
+      </c>
       <c r="J214" s="2" t="n"/>
       <c r="K214" s="3" t="n"/>
       <c r="O214" t="inlineStr">
@@ -15849,7 +16154,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="Q214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>56700000 explored (274048 execs, 56425952 blocked)</t>
+        </is>
+      </c>
       <c r="R214" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 13 --horizon 34 --keep-going --workers 7</t>
@@ -16590,11 +16899,18 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="n"/>
-      <c r="G226" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>43313069</v>
+      </c>
+      <c r="G226" s="3" t="n">
+        <v>64555.2</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
       <c r="I226" t="inlineStr">
         <is>
           <t>FIRE (first violation)</t>
@@ -16608,6 +16924,9 @@
         <is>
           <t>1</t>
         </is>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
       </c>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
@@ -17227,16 +17546,29 @@
       <c r="G237" s="3" t="n">
         <v>1130.3</v>
       </c>
-      <c r="H237" t="n">
+      <c r="H237" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J237" s="2" t="n"/>
-      <c r="K237" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="n">
+        <v>797662668</v>
+      </c>
+      <c r="K237" s="3" t="n">
+        <v>106294.4</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>8872170</v>
+      </c>
+      <c r="M237" t="n">
+        <v>849.54</v>
+      </c>
+      <c r="N237" t="n">
+        <v>94.04000000000001</v>
+      </c>
       <c r="O237" t="inlineStr">
         <is>
           <t>1</t>
@@ -17407,11 +17739,24 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J240" s="2" t="n"/>
-      <c r="K240" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="n">
+        <v>965129947</v>
+      </c>
+      <c r="K240" s="3" t="n">
+        <v>103482.8</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="n">
+        <v>1350.42</v>
+      </c>
+      <c r="N240" t="n">
+        <v>211.75</v>
+      </c>
       <c r="O240" t="inlineStr">
         <is>
           <t>1</t>
@@ -18943,16 +19288,29 @@
       <c r="G265" s="3" t="n">
         <v>192.6</v>
       </c>
-      <c r="H265" t="n">
+      <c r="H265" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J265" s="2" t="n"/>
-      <c r="K265" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="n">
+        <v>817570043</v>
+      </c>
+      <c r="K265" s="3" t="n">
+        <v>115685.2</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>27788792</v>
+      </c>
+      <c r="M265" t="n">
+        <v>5453.23</v>
+      </c>
+      <c r="N265" t="n">
+        <v>600.65</v>
+      </c>
       <c r="O265" t="inlineStr">
         <is>
           <t>4</t>
@@ -19075,11 +19433,16 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J267" s="2" t="n"/>
-      <c r="K267" s="3" t="n"/>
+      <c r="K267" s="3" t="n">
+        <v>95493.60000000001</v>
+      </c>
+      <c r="N267" t="n">
+        <v>104.56</v>
+      </c>
       <c r="O267" t="inlineStr">
         <is>
           <t>4</t>
@@ -19088,7 +19451,11 @@
       <c r="P267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>408500000 explored (5165424 execs, 403334576 blocked)</t>
+        </is>
+      </c>
       <c r="R267" t="inlineStr">
         <is>
           <t>--mode timed --txns 8 --retries 4 --l 1 --u 5 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -21367,11 +21734,18 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F302" s="2" t="n"/>
-      <c r="G302" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>129402310</v>
+      </c>
+      <c r="G302" s="3" t="n">
+        <v>74552.89999999999</v>
+      </c>
+      <c r="H302" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I302" t="inlineStr">
         <is>
           <t>finished</t>
@@ -21383,13 +21757,22 @@
       <c r="K302" s="3" t="n">
         <v>13501.6</v>
       </c>
-      <c r="L302" t="n">
+      <c r="L302" s="5" t="n">
         <v>28697812</v>
       </c>
+      <c r="M302" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N302" t="n">
+        <v>0.18</v>
+      </c>
       <c r="O302" t="inlineStr">
         <is>
           <t>1</t>
         </is>
+      </c>
+      <c r="P302" t="n">
+        <v>0</v>
       </c>
       <c r="Q302" t="inlineStr"/>
       <c r="R302" t="inlineStr">
@@ -23557,11 +23940,16 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J335" s="2" t="n"/>
-      <c r="K335" s="3" t="n"/>
+      <c r="K335" s="3" t="n">
+        <v>129048.8</v>
+      </c>
+      <c r="N335" t="n">
+        <v>124.26</v>
+      </c>
       <c r="O335" t="inlineStr">
         <is>
           <t>1</t>
@@ -23570,7 +23958,11 @@
       <c r="P335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="inlineStr"/>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>886000000 explored (109507781 execs, 776492219 blocked)</t>
+        </is>
+      </c>
       <c r="R335" t="inlineStr">
         <is>
           <t>--mode timed --ams 2 --queue-size 3 --deadline 8 --u 0 --horizon 12 --keep-going</t>
@@ -23610,11 +24002,16 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J336" s="2" t="n"/>
-      <c r="K336" s="3" t="n"/>
+      <c r="K336" s="3" t="n">
+        <v>129057.8</v>
+      </c>
+      <c r="N336" t="n">
+        <v>345.44</v>
+      </c>
       <c r="O336" t="inlineStr">
         <is>
           <t>1</t>
@@ -23623,7 +24020,11 @@
       <c r="P336" t="n">
         <v>0</v>
       </c>
-      <c r="Q336" t="inlineStr"/>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>1009600000 explored (75748974 execs, 933851026 blocked)</t>
+        </is>
+      </c>
       <c r="R336" t="inlineStr">
         <is>
           <t>--mode timed --ams 3 --queue-size 4 --deadline 8 --u 0 --horizon 7 --keep-going</t>
@@ -24482,11 +24883,16 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="J350" s="2" t="n"/>
-      <c r="K350" s="3" t="n"/>
+      <c r="K350" s="3" t="n">
+        <v>151429.3</v>
+      </c>
+      <c r="N350" t="n">
+        <v>41.46</v>
+      </c>
       <c r="O350" t="inlineStr">
         <is>
           <t>1</t>
@@ -24495,7 +24901,11 @@
       <c r="P350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="inlineStr"/>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>67600000 explored (33800000 execs, 33800000 blocked)</t>
+        </is>
+      </c>
       <c r="R350" t="inlineStr">
         <is>
           <t>--mode timed --participants 2 --rounds 3 --u 20 --w-ratio 3 --sd-ratio 0.25</t>
@@ -25269,11 +25679,18 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="F362" s="2" t="n"/>
-      <c r="G362" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="n">
+        <v>212520833</v>
+      </c>
+      <c r="G362" s="3" t="n">
+        <v>81070.89999999999</v>
+      </c>
+      <c r="H362" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I362" t="inlineStr">
         <is>
           <t>finished</t>
@@ -25285,13 +25702,22 @@
       <c r="K362" s="3" t="n">
         <v>8409.299999999999</v>
       </c>
-      <c r="L362" t="n">
+      <c r="L362" s="5" t="n">
         <v>20007188</v>
       </c>
+      <c r="M362" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="N362" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O362" t="inlineStr">
         <is>
           <t>8</t>
         </is>
+      </c>
+      <c r="P362" t="n">
+        <v>0</v>
       </c>
       <c r="Q362" t="inlineStr"/>
       <c r="R362" t="inlineStr">
@@ -25323,24 +25749,40 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>DNF</t>
         </is>
       </c>
       <c r="F363" s="2" t="n"/>
-      <c r="G363" s="3" t="n"/>
+      <c r="G363" s="3" t="n">
+        <v>141112</v>
+      </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="J363" s="2" t="n"/>
-      <c r="K363" s="3" t="n"/>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="n">
+        <v>2832206904</v>
+      </c>
+      <c r="K363" s="3" t="n">
+        <v>91323.5</v>
+      </c>
+      <c r="L363" t="n">
+        <v>0</v>
+      </c>
+      <c r="N363" t="n">
+        <v>0.65</v>
+      </c>
       <c r="O363" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q363" t="inlineStr"/>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>60000000 explored (11407482 execs, 48592518 blocked)</t>
+        </is>
+      </c>
       <c r="R363" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 6 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --keep-going --parallel shared</t>
@@ -26361,9 +26803,9 @@
           <t>finished 5,773 s, 27,831,855 explored, viol 0</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>running</t>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>DNF 141,112 s (60000000 explored (11407482 execs, 48592518 blocked))</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -26407,7 +26849,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>finished 91,324 s, 2,832,206,904 explored, viol 0</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr"/>
@@ -26595,7 +27037,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>finished 81,071 s, 212,520,833 explored, viol 0</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
@@ -26749,9 +27191,9 @@
       <c r="K40" s="6" t="inlineStr"/>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr"/>
-      <c r="N40" s="6" t="inlineStr">
-        <is>
-          <t>running</t>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>DNF 141,418 s (96300000 explored (397160 execs, 95902840 blocked))</t>
         </is>
       </c>
     </row>
@@ -26773,9 +27215,9 @@
       <c r="K41" s="6" t="inlineStr"/>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
-        <is>
-          <t>running</t>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>DNF 119,254 s (636600000 explored (98154 execs, 636501846 blocked))</t>
         </is>
       </c>
     </row>
@@ -27306,7 +27748,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>finished 91,162 s, 296,781,933 explored, viol 0</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -27331,7 +27773,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>finished 79,486 s, 148,678,165 explored, viol 0</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
@@ -27346,7 +27788,7 @@
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>finished 85,294 s, 105,986,347 explored, viol 0</t>
         </is>
       </c>
       <c r="T6" s="6" t="inlineStr">
@@ -27356,7 +27798,7 @@
       </c>
       <c r="U6" s="6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>finished 89,371 s, 98,579,689 explored, viol 0</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
@@ -27366,12 +27808,12 @@
       </c>
       <c r="W6" s="6" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="X6" s="6" t="inlineStr">
-        <is>
-          <t>running</t>
+          <t>finished 107,700 s, 97,875,995 explored, viol 0</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>DNF 151,797 s (113900000 explored (2188 execs, 113897812 blocked))</t>
         </is>
       </c>
     </row>
@@ -27491,9 +27933,9 @@
           <t>finished 14,651 s, 71,250,086 explored, viol 48,006,837</t>
         </is>
       </c>
-      <c r="X7" s="6" t="inlineStr">
-        <is>
-          <t>running</t>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>DNF 151,797 s (860600000 explored (78126 execs, 860521874 blocked))</t>
         </is>
       </c>
     </row>
@@ -27826,7 +28268,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>finished 71,242 s, 205,078,132 explored, viol 0</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr"/>

--- a/benchmarks/v8/results_v8.xlsx
+++ b/benchmarks/v8/results_v8.xlsx
@@ -2073,7 +2073,6 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2102,7 +2101,6 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2539,7 +2537,6 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -2609,7 +2606,6 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>--clients 6 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -2679,7 +2675,6 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --parallel shared</t>
@@ -2749,7 +2744,6 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>--clients 6 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --parallel shared</t>
@@ -2816,7 +2810,6 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going</t>
@@ -2883,7 +2876,6 @@
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2</t>
@@ -2953,7 +2945,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>--clients 3 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going</t>
@@ -3023,7 +3014,6 @@
       <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>--clients 3 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2</t>
@@ -3093,7 +3083,6 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>--clients 4 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going</t>
@@ -3163,7 +3152,6 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>--clients 4 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2</t>
@@ -3233,7 +3221,6 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>--clients 4 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -3303,7 +3290,6 @@
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>--clients 4 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --parallel shared</t>
@@ -3373,7 +3359,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going</t>
@@ -3443,7 +3428,6 @@
       <c r="P15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2</t>
@@ -3513,7 +3497,6 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>--clients 4 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0 --ttl-ratio 5 --fencing off --pause-ratio 4.5 --keep-going</t>
@@ -3583,7 +3566,6 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0 --ttl-ratio 5 --fencing off --pause-ratio 4.5 --keep-going --parallel shared</t>
@@ -3653,7 +3635,6 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>--clients 6 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0 --ttl-ratio 5 --fencing off --pause-ratio 4.5 --keep-going --parallel shared</t>
@@ -3723,7 +3704,6 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>--clients 4 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0 --ttl-ratio 5 --fencing on --pause-ratio 5</t>
@@ -3793,7 +3773,6 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0 --ttl-ratio 5 --fencing on --pause-ratio 5 --parallel shared</t>
@@ -3863,7 +3842,6 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>--clients 6 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0 --ttl-ratio 5 --fencing on --pause-ratio 5 --parallel shared</t>
@@ -3903,7 +3881,7 @@
         <v>263.3</v>
       </c>
       <c r="H22" t="n">
-        <v>63158</v>
+        <v>48240</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3933,7 +3911,11 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Timed violations re-run with e96fe7a (2026-10-07): 48240 (campaign 63158 double-counted the prefix of executions whose delivered send was rejected); explored unchanged</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 2 --keep-going --parallel shared</t>
@@ -4003,7 +3985,6 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 3.5 --keep-going --parallel shared</t>
@@ -4043,7 +4024,7 @@
         <v>384.8</v>
       </c>
       <c r="H24" t="n">
-        <v>55048</v>
+        <v>41760</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4073,7 +4054,11 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Timed violations re-run with e96fe7a (2026-10-07): 41760 (campaign 55048 double-counted the prefix of executions whose delivered send was rejected); explored unchanged</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 4 --keep-going --parallel shared</t>
@@ -4143,7 +4128,6 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0 --ttl-ratio 5 --fencing off --pause-ratio 2.5 --keep-going --parallel shared</t>
@@ -4183,7 +4167,7 @@
         <v>198.5</v>
       </c>
       <c r="H26" t="n">
-        <v>50058</v>
+        <v>34416</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4213,7 +4197,11 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Timed violations re-run with e96fe7a (2026-10-07): 34416 (campaign 50058 double-counted the prefix of executions whose delivered send was rejected); explored unchanged</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0 --ttl-ratio 5 --fencing off --pause-ratio 3 --keep-going --parallel shared</t>
@@ -4283,7 +4271,6 @@
       <c r="P27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 1 --l-ratio 0 --sd-ratio 1 --ttl-ratio 6 --fencing off --pause-ratio 1 --keep-going --parallel shared</t>
@@ -4323,7 +4310,7 @@
         <v>262</v>
       </c>
       <c r="H28" t="n">
-        <v>63158</v>
+        <v>48240</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4353,7 +4340,11 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Timed violations re-run with e96fe7a (2026-10-07): 48240 (campaign 63158 double-counted the prefix of executions whose delivered send was rejected); explored unchanged</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 1 --l-ratio 0 --sd-ratio 1 --ttl-ratio 6 --fencing off --pause-ratio 2 --keep-going --parallel shared</t>
@@ -4393,7 +4384,7 @@
         <v>280.5</v>
       </c>
       <c r="H29" t="n">
-        <v>43100</v>
+        <v>29160</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4423,7 +4414,11 @@
       <c r="P29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Timed violations re-run with e96fe7a (2026-10-07): 29160 (campaign 43100 double-counted the prefix of executions whose delivered send was rejected); explored unchanged</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>--clients 5 --rounds 1 --mode timed --u 2 --l-ratio 1 --sd-ratio 0 --ttl-ratio 5 --fencing off --pause-ratio 5 --keep-going --parallel shared</t>
@@ -4474,7 +4469,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>--clients 6 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 2</t>
@@ -4533,7 +4527,6 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>--clients 4 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5</t>
@@ -4573,7 +4566,7 @@
         <v>13516.5</v>
       </c>
       <c r="H32" t="n">
-        <v>2247921</v>
+        <v>1731960</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -4603,7 +4596,11 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Timed violations re-run with e96fe7a (2026-10-08, brain05): 1731960 (campaign 2247921 double-counted the prefix of executions whose delivered send was rejected); explored unchanged</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>--clients 6 --rounds 1 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 2 --keep-going --parallel shared</t>
@@ -4731,7 +4728,6 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 6 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -4801,7 +4797,6 @@
       <c r="P35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 3 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -4871,7 +4866,6 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>--mode timed --nodes 5 --rounds 2 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -4941,7 +4935,6 @@
       <c r="P37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>--mode timed --nodes 6 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -5011,7 +5004,6 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 9 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -5081,7 +5073,6 @@
       <c r="P39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>--mode timed --nodes 7 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -5151,7 +5142,6 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 4 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -5221,7 +5211,6 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 6 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 2.5 --keep-going</t>
@@ -5272,7 +5261,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 6 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 2.5</t>
@@ -5331,7 +5319,6 @@
       <c r="P43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 6 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0</t>
@@ -5401,7 +5388,6 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 6 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 2.5 --keep-going</t>
@@ -5452,7 +5438,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 6 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 2.5</t>
@@ -5522,7 +5507,6 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>--mode timed --nodes 8 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -5592,7 +5576,6 @@
       <c r="P47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 10 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -5662,7 +5645,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 5 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -5732,7 +5714,6 @@
       <c r="P49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 5 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -5802,7 +5783,6 @@
       <c r="P50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>--mode timed --nodes 5 --rounds 3 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -5872,7 +5852,6 @@
       <c r="P51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>--mode timed --nodes 6 --rounds 2 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -5942,7 +5921,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 10 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -6012,7 +5990,6 @@
       <c r="P53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
           <t>--mode timed --nodes 8 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6082,7 +6059,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>--mode timed --nodes 5 --rounds 3 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6152,7 +6128,6 @@
       <c r="P55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>--mode timed --nodes 6 --rounds 2 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6222,7 +6197,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 9 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -6292,7 +6266,6 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 4 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6362,7 +6335,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 7 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -6432,7 +6404,6 @@
       <c r="P59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 8 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going --parallel shared</t>
@@ -6502,7 +6473,6 @@
       <c r="P60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 8 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 2.5 --keep-going --parallel shared</t>
@@ -6572,7 +6542,6 @@
       <c r="P61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
           <t>--mode timed --nodes 5 --rounds 2 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 2.5 --keep-going</t>
@@ -6642,7 +6611,6 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 6 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6712,7 +6680,6 @@
       <c r="P63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 3 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6782,7 +6749,6 @@
       <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
           <t>--mode timed --nodes 5 --rounds 2 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6852,7 +6818,6 @@
       <c r="P65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
           <t>--mode timed --nodes 6 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6922,7 +6887,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>--mode timed --nodes 7 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0.5 --w-suspect-ratio 3.0 --keep-going</t>
@@ -6989,7 +6953,6 @@
       <c r="P67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7059,7 +7022,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 2 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7129,7 +7091,6 @@
       <c r="P69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 3 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7199,7 +7160,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 4 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7269,7 +7229,6 @@
       <c r="P71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 5 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7339,7 +7298,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7409,7 +7367,6 @@
       <c r="P73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 2 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7479,7 +7436,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
           <t>--mode timed --nodes 5 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7549,7 +7505,6 @@
       <c r="P75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --rounds 6 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7619,7 +7574,6 @@
       <c r="P76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
           <t>--mode timed --nodes 4 --rounds 3 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7689,7 +7643,6 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>--mode timed --nodes 5 --rounds 2 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7759,7 +7712,6 @@
       <c r="P78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
           <t>--mode timed --nodes 6 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7829,7 +7781,6 @@
       <c r="P79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
           <t>--mode timed --nodes 7 --rounds 1 --u 2 --sd-ratio 0.5 --w-probe-ratio 1 --l-ratio 0 --w-suspect-ratio 3.0 --keep-going</t>
@@ -7957,7 +7908,6 @@
       <c r="P81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 2 --readings danger --keep-going</t>
@@ -8027,7 +7977,6 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 1 --readings danger --keep-going</t>
@@ -8097,7 +8046,6 @@
       <c r="P83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
           <t>--mode timed --period-ratio 6 --keep-going</t>
@@ -8167,7 +8115,6 @@
       <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>--mode timed --readings safe --property sensor --rounds 3 --keep-going</t>
@@ -8237,7 +8184,6 @@
       <c r="P85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
           <t>--mode timed --period-ratio 5 --keep-going --parallel partitioned</t>
@@ -8307,7 +8253,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 2 --keep-going --parallel partitioned</t>
@@ -8377,7 +8322,6 @@
       <c r="P87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
           <t>--mode timed --keep-going --u 2 --period-ratio 3 --check-ratio 7.5 --ack-deadline-ratio 2.5 --rescue-deadline-ratio 2.5 --obstacle-ratio 0.5</t>
@@ -8447,7 +8391,6 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>--mode timed --keep-going --u 3 --period-ratio 2 --check-ratio 5 --ack-deadline-ratio 1.6666667 --rescue-deadline-ratio 1.6666667 --obstacle-ratio 0.3333333</t>
@@ -8498,7 +8441,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
           <t>--mode timed --u 3 --period-ratio 2 --check-ratio 5 --ack-deadline-ratio 1.6666667 --rescue-deadline-ratio 1.6666667 --obstacle-ratio 0.3333333</t>
@@ -8568,7 +8510,6 @@
       <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
           <t>--mode timed --readings safe --property sensor --rounds 3 --keep-going --l-ratio 0 --u 4 --period-ratio 2.5 --check-ratio 3.75</t>
@@ -8638,7 +8579,6 @@
       <c r="P91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
           <t>--mode timed --readings safe --property sensor --rounds 3 --keep-going --l-ratio 0 --u 5 --period-ratio 2 --check-ratio 3</t>
@@ -8689,7 +8629,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
           <t>--mode timed --readings safe --property sensor --rounds 3 --l-ratio 0 --u 5 --period-ratio 2 --check-ratio 3</t>
@@ -8743,7 +8682,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 1</t>
@@ -8797,7 +8735,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 3-5 --rounds 2</t>
@@ -8859,7 +8796,6 @@
       <c r="P95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 1 --rounds 1 --readings random-relevant --keep-going</t>
@@ -8921,7 +8857,6 @@
       <c r="P96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 2 --rounds 1 --readings random-relevant --keep-going</t>
@@ -8983,7 +8918,6 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 3-5 --rounds 2 --readings random-relevant --keep-going</t>
@@ -9045,7 +8979,6 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 3-6 --rounds 2 --readings random-relevant --keep-going</t>
@@ -9107,7 +9040,6 @@
       <c r="P99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 3-7 --rounds 2 --readings random-relevant --keep-going</t>
@@ -9158,7 +9090,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 3-6 --rounds 4 --sensors 1 --sensor0-period-ratio 50 --readings danger</t>
@@ -9209,7 +9140,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 3-7 --rounds 4 --sensors 1 --sensor0-period-ratio 50 --readings danger</t>
@@ -9279,7 +9209,6 @@
       <c r="P102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 1 --keep-going --parallel partitioned</t>
@@ -9349,7 +9278,6 @@
       <c r="P103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
           <t>--mode timed --readings safe --property sensor --rounds 4 --keep-going --parallel partitioned</t>
@@ -9419,7 +9347,6 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 4 --readings danger --keep-going --parallel partitioned</t>
@@ -9489,7 +9416,6 @@
       <c r="P105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
           <t>--mode timed --sensors 1 --rounds 2 --keep-going --parallel partitioned</t>
@@ -9559,7 +9485,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
           <t>--mode timed --period-ratio 3 --keep-going --parallel partitioned</t>
@@ -9611,7 +9536,6 @@
       <c r="P107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 4 --readings random-relevant --keep-going --parallel partitioned</t>
@@ -9655,8 +9579,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9703,7 +9625,6 @@
       <c r="P109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 2 --rounds 2 --readings random-relevant --keep-going --parallel partitioned</t>
@@ -9747,8 +9668,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9795,7 +9714,6 @@
       <c r="P111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 3-6 --rounds 3 --readings random-relevant --keep-going --parallel partitioned</t>
@@ -9839,8 +9757,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9887,7 +9803,6 @@
       <c r="P113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 3-7 --rounds 3 --readings random-relevant --keep-going --parallel partitioned</t>
@@ -9931,8 +9846,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9979,7 +9892,6 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
           <t>--mode timed --table3-row 2 --readings danger --rounds 2 --keep-going --parallel partitioned</t>
@@ -10031,7 +9943,6 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
           <t>--mode timed --readings safe --property sensor --rounds 5 --keep-going --parallel partitioned</t>
@@ -10075,8 +9986,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10120,7 +10029,6 @@
           <t>100000 explored (6113 execs, 93887 blocked)</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10333,7 +10241,6 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 1 --td 1 --t1 3 --tr 9 --sync 7 --k 2 --files 2 --property p2 --keep-going</t>
@@ -10459,7 +10366,6 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 1 --td 1 --t1 3 --tr 9 --sync 7 --k 2 --files 2 --property p2 --keep-going --workers 6</t>
@@ -10789,7 +10695,6 @@
       <c r="P128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 3 --td 1 --t1 3 --tr 21 --sync 21 --k 2 --files 1 --property all --keep-going --workers 6</t>
@@ -10841,7 +10746,6 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 4 --td 1 --t1 3 --tr 27 --sync 27 --k 2 --files 1 --property all --keep-going --workers 6</t>
@@ -10893,7 +10797,6 @@
       <c r="P130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 5 --td 1 --t1 3 --tr 33 --sync 33 --k 2 --files 1 --property all --keep-going --workers 6</t>
@@ -10945,7 +10848,6 @@
       <c r="P131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 6 --td 1 --t1 3 --tr 39 --sync 39 --k 2 --files 1 --property all --keep-going --workers 6</t>
@@ -10997,7 +10899,6 @@
       <c r="P132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 7 --td 1 --t1 3 --tr 45 --sync 45 --k 2 --files 1 --property all --keep-going --workers 6</t>
@@ -11513,7 +11414,6 @@
       <c r="P140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 1 --td 1 --t1 3 --tr 9 --sync 6 --k 2 --files 2 --property p2 --keep-going</t>
@@ -11565,7 +11465,6 @@
       <c r="P141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 2 --td 1 --t1 3 --tr 15 --sync 13 --k 2 --files 2 --property p2 --keep-going</t>
@@ -11617,7 +11516,6 @@
       <c r="P142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr">
         <is>
           <t>--mode timed --n 2 --max 2 --td 1 --t1 3 --tr 15 --sync 12 --k 2 --files 2 --property p2 --keep-going</t>
@@ -11817,7 +11715,6 @@
       <c r="P145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr">
         <is>
           <t>--mode timed --n 5 --max 1 --td 1 --t1 3 --tr 9 --sync 9 --k 2 --files 1 --property all --keep-going --workers 6</t>
@@ -11940,7 +11837,6 @@
           <t>1885100000 explored (22973507 execs, 1862126493 blocked)</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11984,7 +11880,6 @@
           <t>1725800000 explored (3751296 execs, 1722048704 blocked)</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12049,7 +11944,6 @@
       <c r="P149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 8 --retries 1 --keep-going --parallel shared</t>
@@ -12119,7 +12013,6 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 5 --retries 1 --keep-going</t>
@@ -12189,7 +12082,6 @@
       <c r="P151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 6 --retries 1 --keep-going</t>
@@ -12241,7 +12133,6 @@
       <c r="P152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 10 --retries 1 --keep-going --parallel shared</t>
@@ -12311,7 +12202,6 @@
       <c r="P153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 6 --retries 1 --keep-going --parallel shared</t>
@@ -12381,7 +12271,6 @@
       <c r="P154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 7 --retries 1 --keep-going --parallel shared</t>
@@ -12433,7 +12322,6 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 9 --retries 1 --keep-going --parallel shared</t>
@@ -12503,7 +12391,6 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 4 --retries 2 --keep-going --parallel shared</t>
@@ -12573,7 +12460,6 @@
       <c r="P157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 8 --retries 1 --keep-going --no-errs --parallel shared</t>
@@ -12643,7 +12529,6 @@
       <c r="P158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 9 --retries 1 --keep-going --no-errs --parallel shared</t>
@@ -12713,7 +12598,6 @@
       <c r="P159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 10 --retries 1 --keep-going --no-errs --parallel shared</t>
@@ -12765,7 +12649,6 @@
       <c r="P160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 12 --retries 1 --keep-going --no-errs --parallel shared</t>
@@ -12817,7 +12700,6 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 9 --messages 14 --retries 1 --keep-going --no-errs --parallel shared</t>
@@ -12887,7 +12769,6 @@
       <c r="P162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 7 --messages 5 --retries 1 --keep-going</t>
@@ -12957,7 +12838,6 @@
       <c r="P163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 8 --messages 5 --retries 1 --keep-going</t>
@@ -13027,7 +12907,6 @@
       <c r="P164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr">
         <is>
           <t>--mode timed --dk 30 --dl 30 --dr 10 --to 70 --messages 5 --retries 1 --keep-going</t>
@@ -13097,7 +12976,6 @@
       <c r="P165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr">
         <is>
           <t>--mode timed --dk 30 --dl 30 --dr 10 --to 71 --messages 5 --retries 1 --keep-going</t>
@@ -13167,7 +13045,6 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 3 --to 9 --messages 5 --retries 1 --keep-going</t>
@@ -13237,7 +13114,6 @@
       <c r="P167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 3 --to 10 --messages 5 --retries 1 --keep-going</t>
@@ -13307,7 +13183,6 @@
       <c r="P168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr">
         <is>
           <t>--mode timed --dk 2 --dl 5 --dr 1 --to 8 --messages 5 --retries 1 --keep-going</t>
@@ -13377,7 +13252,6 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr">
         <is>
           <t>--mode timed --dk 2 --dl 5 --dr 1 --to 9 --messages 5 --retries 1 --keep-going</t>
@@ -13447,7 +13321,6 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 7 --messages 6 --retries 1 --keep-going --parallel shared</t>
@@ -13517,7 +13390,6 @@
       <c r="P171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr">
         <is>
           <t>--mode timed --dk 3 --dl 3 --dr 1 --to 8 --messages 6 --retries 1 --keep-going --parallel shared</t>
@@ -13587,7 +13459,6 @@
       <c r="P172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 5 --retries 2 --w-ratio 3</t>
@@ -13657,7 +13528,6 @@
       <c r="P173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr">
         <is>
           <t>--mode timed --variant par --messages 5 --retries 2 --w-ratio 3 --keep-going</t>
@@ -13727,7 +13597,6 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 2 --retries 5 --w-ratio 3</t>
@@ -13779,7 +13648,6 @@
       <c r="P175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 8 --retries 2 --w-ratio 3</t>
@@ -13849,7 +13717,6 @@
       <c r="P176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 3 --retries 2 --w-ratio 3</t>
@@ -13919,7 +13786,6 @@
       <c r="P177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 4 --retries 2 --w-ratio 3</t>
@@ -14037,7 +13903,6 @@
       <c r="P179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 7 --retries 2 --w-ratio 3</t>
@@ -14107,7 +13972,6 @@
       <c r="P180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 2 --retries 4 --w-ratio 3</t>
@@ -14177,7 +14041,6 @@
       <c r="P181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 2 --retries 6 --w-ratio 3</t>
@@ -14295,7 +14158,6 @@
       <c r="P183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 2 --retries 8 --w-ratio 3</t>
@@ -14347,7 +14209,6 @@
       <c r="P184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 2 --retries 9 --w-ratio 3</t>
@@ -14399,7 +14260,6 @@
       <c r="P185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 2 --retries 10 --w-ratio 3</t>
@@ -14469,7 +14329,6 @@
       <c r="P186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr">
         <is>
           <t>--mode timed --variant par --messages 4 --retries 2 --w-ratio 3 --keep-going</t>
@@ -14539,7 +14398,6 @@
       <c r="P187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 4 --retries 2 --w-ratio 2</t>
@@ -14609,7 +14467,6 @@
       <c r="P188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 4 --retries 2 --w-ratio 1</t>
@@ -14679,7 +14536,6 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr">
         <is>
           <t>--mode timed --variant abp --messages 5 --retries 2 --w-ratio 2</t>
@@ -14731,7 +14587,6 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr">
         <is>
           <t>--mode timed --variant par --messages 5 --retries 2 --w-ratio 2 --keep-going</t>
@@ -14783,7 +14638,6 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr">
         <is>
           <t>--mode timed --variant par --messages 5 --retries 2 --u 3 --l-ratio 1 --proc-ratio 0.333 --w-ratio 2.3333333 --keep-going</t>
@@ -14853,7 +14707,6 @@
       <c r="P192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr">
         <is>
           <t>--mode timed --variant par --messages 5 --retries 2 --u 3 --l-ratio 1 --proc-ratio 0.333 --w-ratio 2.6666667 --keep-going</t>
@@ -14905,7 +14758,6 @@
       <c r="P193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr">
         <is>
           <t>--mode timed --variant par --messages 5 --retries 2 --u 3 --l-ratio 1 --proc-ratio 0.333 --w-ratio 1 --keep-going</t>
@@ -14957,7 +14809,6 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
           <t>--mode timed --variant par --messages 5 --retries 2 --u 3 --l-ratio 1 --proc-ratio 0.333 --w-ratio 0.6666667 --keep-going</t>
@@ -15027,7 +14878,6 @@
       <c r="P195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 13 --horizon 22 --keep-going</t>
@@ -15097,7 +14947,6 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 13 --horizon 25 --keep-going --workers 7</t>
@@ -15167,7 +15016,6 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 13 --horizon 31 --keep-going --workers 7</t>
@@ -15237,7 +15085,6 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 13 --horizon 16 --keep-going</t>
@@ -15307,7 +15154,6 @@
       <c r="P199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 13 --horizon 19 --keep-going</t>
@@ -15377,7 +15223,6 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 13 --horizon 28 --keep-going --workers 7</t>
@@ -15426,8 +15271,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15471,8 +15314,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15516,8 +15357,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -15566,7 +15405,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 12 --horizon 25</t>
@@ -15636,7 +15474,6 @@
       <c r="P205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr">
         <is>
           <t>--mode timed --delta 1 --phi 4 --to 13 --horizon 26 --keep-going --workers 7</t>
@@ -15690,7 +15527,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr">
         <is>
           <t>--mode timed --delta 1 --phi 4 --to 12 --horizon 26</t>
@@ -15760,7 +15596,6 @@
       <c r="P207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
         <is>
           <t>--mode timed --delta 3 --phi 4 --to 15 --horizon 24 --keep-going --workers 7</t>
@@ -15814,7 +15649,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr">
         <is>
           <t>--mode timed --delta 3 --phi 4 --to 14 --horizon 24</t>
@@ -15884,7 +15718,6 @@
       <c r="P209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 3 --to 10 --horizon 19 --keep-going</t>
@@ -15938,7 +15771,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 3 --to 9 --horizon 19</t>
@@ -16008,7 +15840,6 @@
       <c r="P211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 2 --to 7 --horizon 14 --keep-going</t>
@@ -16059,7 +15890,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 2 --to 6 --horizon 14</t>
@@ -16110,7 +15940,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr">
         <is>
           <t>--mode timed --delta 2 --phi 4 --to 13 --horizon 25 --control crashed-sender</t>
@@ -16228,7 +16057,6 @@
       <c r="P215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault none --rounds 4 --keep-going</t>
@@ -16298,7 +16126,6 @@
       <c r="P216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault none --rounds 5 --keep-going</t>
@@ -16368,7 +16195,6 @@
       <c r="P217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault none --attack-from-ratio 0 --rounds 3 --keep-going</t>
@@ -16438,7 +16264,6 @@
       <c r="P218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --phase-ratio 11 --keep-going</t>
@@ -16500,7 +16325,6 @@
       <c r="P219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault none --attack-from-ratio 0 --rounds 5</t>
@@ -16562,7 +16386,6 @@
       <c r="P220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault none --attack-from-ratio 0 --rounds 6</t>
@@ -16624,7 +16447,6 @@
       <c r="P221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --fail-a-ratio 50 --rounds 5 --phase-ratio 1</t>
@@ -16686,7 +16508,6 @@
       <c r="P222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --fail-a-ratio 50 --rounds 5 --phase-ratio -3</t>
@@ -16748,7 +16569,6 @@
       <c r="P223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --max-missed 1 --fail-a-ratio 30 --rounds 4 --phase-ratio 1</t>
@@ -16810,7 +16630,6 @@
       <c r="P224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --max-missed 1 --fail-a-ratio 30 --rounds 4 --phase-ratio -3</t>
@@ -16869,7 +16688,6 @@
       <c r="P225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault none --rounds 10</t>
@@ -16928,7 +16746,6 @@
       <c r="P226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 8 --phase-ratio 11</t>
@@ -16998,7 +16815,6 @@
       <c r="P227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault none --rounds 6 --keep-going</t>
@@ -17052,7 +16868,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --fail-a-ratio 50 --rounds 5 --phase-ratio 0</t>
@@ -17106,7 +16921,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --fail-a-ratio 50 --rounds 5 --phase-ratio -2</t>
@@ -17160,7 +16974,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --max-missed 1 --fail-a-ratio 30 --rounds 4 --phase-ratio -2</t>
@@ -17222,7 +17035,6 @@
       <c r="P231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr">
         <is>
           <t>--mode timed --variant noopt --fault switch --rounds 4</t>
@@ -17281,7 +17093,6 @@
       <c r="P232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault none --rounds 8</t>
@@ -17340,7 +17151,6 @@
       <c r="P233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 6 --phase-ratio 11</t>
@@ -17394,7 +17204,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --max-missed 1 --fail-a-ratio 30 --rounds 4 --phase-ratio -1</t>
@@ -17448,7 +17257,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault link --attack-from-ratio 0 --max-missed 1 --fail-a-ratio 30 --rounds 4 --phase-ratio 0</t>
@@ -17507,7 +17315,6 @@
       <c r="P236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 5 --phase-ratio 11</t>
@@ -17577,7 +17384,6 @@
       <c r="P237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault none --rounds 7 --keep-going</t>
@@ -17636,7 +17442,6 @@
       <c r="P238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 5 --fail-a-ratio 11 --sep-ratio 41</t>
@@ -17695,7 +17500,6 @@
       <c r="P239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --phase-ratio 13</t>
@@ -17765,7 +17569,6 @@
       <c r="P240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr">
         <is>
           <t>--mode timed --variant leasing --fault none --attack-from-ratio 0 --rounds 4 --keep-going</t>
@@ -17824,7 +17627,6 @@
       <c r="P241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --hb-on-nrp-change on --fail-a-ratio 1 --sep-ratio 11</t>
@@ -17883,7 +17685,6 @@
       <c r="P242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --u 2 --l-ratio 0.5 --phase-ratio 10.5</t>
@@ -17942,7 +17743,6 @@
       <c r="P243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --u 2 --l-ratio 0.5 --phase-ratio 11.5</t>
@@ -18001,7 +17801,6 @@
       <c r="P244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --fail-a-ratio 31 --sep-ratio -21</t>
@@ -18052,7 +17851,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 5 --fail-a-ratio 11 --sep-ratio 40</t>
@@ -18103,7 +17901,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --fail-a-ratio 31 --sep-ratio -20</t>
@@ -18154,7 +17951,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --phase-ratio 10</t>
@@ -18205,7 +18001,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --phase-ratio 14</t>
@@ -18256,7 +18051,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --u 2 --l-ratio 0.5 --phase-ratio 10</t>
@@ -18307,7 +18101,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --u 2 --l-ratio 0.5 --phase-ratio 12</t>
@@ -18358,7 +18151,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --l-ratio 0 --phase-ratio 11</t>
@@ -18409,7 +18201,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr">
         <is>
           <t>--mode timed --variant nrp --fault switch --rounds 4 --hb-on-nrp-change on --fail-a-ratio 1 --sep-ratio 10</t>
@@ -18479,7 +18270,6 @@
       <c r="P253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="inlineStr"/>
       <c r="R253" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 5 --w 1 --backoff 0 --keep-going</t>
@@ -18549,7 +18339,6 @@
       <c r="P254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 5 --l 1 --u 5 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -18619,7 +18408,6 @@
       <c r="P255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 1 --l 1 --u 5 --w 1 --backoff 0 --keep-going</t>
@@ -18689,7 +18477,6 @@
       <c r="P256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 2 --l 1 --u 5 --w 1 --backoff 0 --keep-going</t>
@@ -18759,7 +18546,6 @@
       <c r="P257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 4 --l 1 --u 5 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -18829,7 +18615,6 @@
       <c r="P258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr">
         <is>
           <t>--mode timed --txns 16 --retries 1 --l 1 --u 5 --w 1 --backoff 0 --keep-going</t>
@@ -18899,7 +18684,6 @@
       <c r="P259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="inlineStr"/>
       <c r="R259" t="inlineStr">
         <is>
           <t>--mode timed --txns 64 --retries 1 --l 1 --u 5 --w 1 --backoff 0 --keep-going</t>
@@ -18969,7 +18753,6 @@
       <c r="P260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr">
         <is>
           <t>--mode timed --txns 8 --retries 2 --l 1 --u 5 --w 1 --backoff 0 --keep-going</t>
@@ -19039,7 +18822,6 @@
       <c r="P261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr">
         <is>
           <t>--mode timed --txns 16 --retries 2 --l 1 --u 5 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -19109,7 +18891,6 @@
       <c r="P262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr">
         <is>
           <t>--mode timed --txns 32 --retries 2 --l 1 --u 5 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -19179,7 +18960,6 @@
       <c r="P263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="inlineStr"/>
       <c r="R263" t="inlineStr">
         <is>
           <t>--mode timed --txns 4 --retries 3 --l 1 --u 5 --w 1 --backoff 0 --keep-going</t>
@@ -19249,7 +19029,6 @@
       <c r="P264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="inlineStr"/>
       <c r="R264" t="inlineStr">
         <is>
           <t>--mode timed --txns 8 --retries 3 --l 1 --u 5 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -19319,7 +19098,6 @@
       <c r="P265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="inlineStr"/>
       <c r="R265" t="inlineStr">
         <is>
           <t>--mode timed --txns 16 --retries 3 --l 1 --u 5 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -19389,7 +19167,6 @@
       <c r="P266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="inlineStr"/>
       <c r="R266" t="inlineStr">
         <is>
           <t>--mode timed --txns 4 --retries 4 --l 1 --u 5 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -19525,7 +19302,6 @@
       <c r="P268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 6 --w 1 --backoff 0 --keep-going</t>
@@ -19595,7 +19371,6 @@
       <c r="P269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="inlineStr"/>
       <c r="R269" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 7 --w 1 --backoff 0 --keep-going</t>
@@ -19665,7 +19440,6 @@
       <c r="P270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="inlineStr"/>
       <c r="R270" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 8 --w 1 --backoff 0 --keep-going</t>
@@ -19735,7 +19509,6 @@
       <c r="P271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="inlineStr"/>
       <c r="R271" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 7 --w 1 --backoff 2 --keep-going</t>
@@ -19805,7 +19578,6 @@
       <c r="P272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="inlineStr"/>
       <c r="R272" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 8 --w 1 --backoff 2 --keep-going</t>
@@ -19875,7 +19647,6 @@
       <c r="P273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="inlineStr"/>
       <c r="R273" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 9 --w 1 --backoff 2 --keep-going</t>
@@ -19945,7 +19716,6 @@
       <c r="P274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="inlineStr"/>
       <c r="R274" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 10 --w 1 --backoff 2 --keep-going</t>
@@ -20015,7 +19785,6 @@
       <c r="P275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 2 --u 10 --w 1 --backoff 0 --keep-going</t>
@@ -20085,7 +19854,6 @@
       <c r="P276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="inlineStr"/>
       <c r="R276" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 2 --u 11 --w 1 --backoff 0 --keep-going</t>
@@ -20155,7 +19923,6 @@
       <c r="P277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 2 --u 14 --w 1 --backoff 0 --keep-going</t>
@@ -20225,7 +19992,6 @@
       <c r="P278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="inlineStr"/>
       <c r="R278" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 2 --u 15 --w 1 --backoff 0 --keep-going</t>
@@ -20295,7 +20061,6 @@
       <c r="P279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="inlineStr"/>
       <c r="R279" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 9 --w 5 --backoff 0 --keep-going</t>
@@ -20365,7 +20130,6 @@
       <c r="P280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="inlineStr"/>
       <c r="R280" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 10 --w 5 --backoff 0 --keep-going</t>
@@ -20435,7 +20199,6 @@
       <c r="P281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="inlineStr"/>
       <c r="R281" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 11 --w 5 --backoff 0 --keep-going</t>
@@ -20505,7 +20268,6 @@
       <c r="P282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="inlineStr"/>
       <c r="R282" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 12 --w 5 --backoff 0 --keep-going</t>
@@ -20575,7 +20337,6 @@
       <c r="P283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="inlineStr"/>
       <c r="R283" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 4 --l 1 --u 6 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -20645,7 +20406,6 @@
       <c r="P284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="inlineStr"/>
       <c r="R284" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 4 --l 1 --u 7 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -20715,7 +20475,6 @@
       <c r="P285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="inlineStr"/>
       <c r="R285" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 4 --l 1 --u 8 --w 1 --backoff 0 --keep-going --parallel shared</t>
@@ -20785,7 +20544,6 @@
       <c r="P286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="inlineStr"/>
       <c r="R286" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 4 --l 1 --u 9 --w 5 --backoff 0 --keep-going --parallel shared</t>
@@ -20855,7 +20613,6 @@
       <c r="P287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="inlineStr"/>
       <c r="R287" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 8 --w 1 --backoff 0 --fix epoch-bump --keep-going</t>
@@ -20925,7 +20682,6 @@
       <c r="P288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 4 --l 1 --u 8 --w 1 --backoff 0 --fix epoch-bump --keep-going --parallel shared</t>
@@ -20987,7 +20743,6 @@
       <c r="P289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 5 --w 1 --backoff 0</t>
@@ -21041,7 +20796,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q290" t="inlineStr"/>
       <c r="R290" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 6 --w 1 --backoff 0</t>
@@ -21095,7 +20849,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q291" t="inlineStr"/>
       <c r="R291" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 8 --w 1 --backoff 0</t>
@@ -21149,7 +20902,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q292" t="inlineStr"/>
       <c r="R292" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 8 --w 1 --backoff 2</t>
@@ -21200,7 +20952,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q293" t="inlineStr"/>
       <c r="R293" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 3 --l 1 --u 10 --w 1 --backoff 2</t>
@@ -21262,7 +21013,6 @@
       <c r="P294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="inlineStr"/>
       <c r="R294" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 4 --l 1 --u 5 --w 1 --backoff 0</t>
@@ -21316,7 +21066,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q295" t="inlineStr"/>
       <c r="R295" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 4 --l 1 --u 8 --w 1 --backoff 0</t>
@@ -21370,7 +21119,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q296" t="inlineStr"/>
       <c r="R296" t="inlineStr">
         <is>
           <t>--mode timed --txns 2 --retries 5 --l 1 --u 8 --w 1 --backoff 0</t>
@@ -21424,7 +21172,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q297" t="inlineStr"/>
       <c r="R297" t="inlineStr">
         <is>
           <t>--mode timed --txns 32 --retries 2 --l 1 --u 8 --w 1 --backoff 0</t>
@@ -21494,7 +21241,6 @@
       <c r="P298" t="n">
         <v>0</v>
       </c>
-      <c r="Q298" t="inlineStr"/>
       <c r="R298" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 14 --forward-delay-ratio 43</t>
@@ -21564,7 +21310,6 @@
       <c r="P299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="inlineStr"/>
       <c r="R299" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 14 --forward-delay-ratio 26</t>
@@ -21634,7 +21379,6 @@
       <c r="P300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="inlineStr"/>
       <c r="R300" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 10 --forward-delay-ratio 35</t>
@@ -21704,7 +21448,6 @@
       <c r="P301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="inlineStr"/>
       <c r="R301" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 10 --forward-delay-ratio 18</t>
@@ -21774,7 +21517,6 @@
       <c r="P302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="inlineStr"/>
       <c r="R302" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 15 --forward-delay-ratio 45</t>
@@ -21844,7 +21586,6 @@
       <c r="P303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="inlineStr"/>
       <c r="R303" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 15 --l-ratio 1 --forward-delay-ratio 26</t>
@@ -21914,7 +21655,6 @@
       <c r="P304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="inlineStr"/>
       <c r="R304" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 14 --l-ratio 1 --forward-delay-ratio 24</t>
@@ -21984,7 +21724,6 @@
       <c r="P305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="inlineStr"/>
       <c r="R305" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 13 --forward-delay-ratio 24</t>
@@ -22054,7 +21793,6 @@
       <c r="P306" t="n">
         <v>0</v>
       </c>
-      <c r="Q306" t="inlineStr"/>
       <c r="R306" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 13 --forward-delay-ratio 41</t>
@@ -22124,7 +21862,6 @@
       <c r="P307" t="n">
         <v>0</v>
       </c>
-      <c r="Q307" t="inlineStr"/>
       <c r="R307" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 13 --l-ratio 1 --forward-delay-ratio 22</t>
@@ -22194,7 +21931,6 @@
       <c r="P308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="inlineStr"/>
       <c r="R308" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 12 --forward-delay-ratio 22</t>
@@ -22264,7 +22000,6 @@
       <c r="P309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="inlineStr"/>
       <c r="R309" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 12 --forward-delay-ratio 39</t>
@@ -22334,7 +22069,6 @@
       <c r="P310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="inlineStr"/>
       <c r="R310" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 12 --l-ratio 1 --forward-delay-ratio 20</t>
@@ -22404,7 +22138,6 @@
       <c r="P311" t="n">
         <v>0</v>
       </c>
-      <c r="Q311" t="inlineStr"/>
       <c r="R311" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 11 --forward-delay-ratio 20</t>
@@ -22474,7 +22207,6 @@
       <c r="P312" t="n">
         <v>0</v>
       </c>
-      <c r="Q312" t="inlineStr"/>
       <c r="R312" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 11 --forward-delay-ratio 37</t>
@@ -22544,7 +22276,6 @@
       <c r="P313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="inlineStr"/>
       <c r="R313" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 10 --l-ratio 1 --forward-delay-ratio 16</t>
@@ -22614,7 +22345,6 @@
       <c r="P314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="inlineStr"/>
       <c r="R314" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 12 --forward-delay-ratio 38</t>
@@ -22684,7 +22414,6 @@
       <c r="P315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="inlineStr"/>
       <c r="R315" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 12 --forward-delay-ratio 21</t>
@@ -22754,7 +22483,6 @@
       <c r="P316" t="n">
         <v>0</v>
       </c>
-      <c r="Q316" t="inlineStr"/>
       <c r="R316" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 10 --forward-delay-ratio 34</t>
@@ -22824,7 +22552,6 @@
       <c r="P317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="inlineStr"/>
       <c r="R317" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 10 --forward-delay-ratio 17</t>
@@ -22894,7 +22621,6 @@
       <c r="P318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="inlineStr"/>
       <c r="R318" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 10 --sd-ratio 1 --forward-delay-ratio 36</t>
@@ -22964,7 +22690,6 @@
       <c r="P319" t="n">
         <v>0</v>
       </c>
-      <c r="Q319" t="inlineStr"/>
       <c r="R319" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --keep-going --rounds 10 --sd-ratio 1 --forward-delay-ratio 37</t>
@@ -23034,7 +22759,6 @@
       <c r="P320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="inlineStr"/>
       <c r="R320" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 10 --sd-ratio 1 --forward-delay-ratio 18</t>
@@ -23104,7 +22828,6 @@
       <c r="P321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="inlineStr"/>
       <c r="R321" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 10 --sd-ratio 1 --forward-delay-ratio 19</t>
@@ -23174,7 +22897,6 @@
       <c r="P322" t="n">
         <v>0</v>
       </c>
-      <c r="Q322" t="inlineStr"/>
       <c r="R322" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --keep-going --rounds 10 --l-ratio 1 --forward-delay-ratio 15</t>
@@ -23225,7 +22947,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q323" t="inlineStr"/>
       <c r="R323" t="inlineStr">
         <is>
           <t>--mode timed --scenario link-up --rounds 10 --forward-delay-ratio 34</t>
@@ -23276,7 +22997,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q324" t="inlineStr"/>
       <c r="R324" t="inlineStr">
         <is>
           <t>--mode timed --scenario lost-hellos --rounds 10 --forward-delay-ratio 17</t>
@@ -23289,7 +23009,6 @@
           <t>Retail saga</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr"/>
       <c r="C325" t="inlineStr">
         <is>
           <t>v2 C=2 N=2 R=5 S=20 U=1 D=7 (hold side, biggest)</t>
@@ -23342,7 +23061,6 @@
       <c r="P325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="inlineStr"/>
       <c r="R325" t="inlineStr">
         <is>
           <t>--mode timed --variant v2 --rounds 5 --stock 20 --u 1 --deadline-ratio 7 --keep-going</t>
@@ -23355,7 +23073,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
         <is>
           <t>K=2 QS=3 DD=8 U=0 H=10 (hold side, biggest two-sided)</t>
@@ -23408,7 +23125,6 @@
       <c r="P326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="inlineStr"/>
       <c r="R326" t="inlineStr">
         <is>
           <t>--mode timed --ams 2 --queue-size 3 --deadline 8 --u 0 --horizon 10 --keep-going</t>
@@ -23421,7 +23137,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
         <is>
           <t>K=2 QS=3 DD=8 U=0 H=8 (hold side)</t>
@@ -23474,7 +23189,6 @@
       <c r="P327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="inlineStr"/>
       <c r="R327" t="inlineStr">
         <is>
           <t>--mode timed --ams 2 --queue-size 3 --deadline 8 --u 0 --horizon 8 --keep-going</t>
@@ -23487,7 +23201,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
         <is>
           <t>K=1 QS=2 DD=8 U=0 H=12 (hold side)</t>
@@ -23540,7 +23253,6 @@
       <c r="P328" t="n">
         <v>0</v>
       </c>
-      <c r="Q328" t="inlineStr"/>
       <c r="R328" t="inlineStr">
         <is>
           <t>--mode timed --ams 1 --deadline 8 --u 0 --horizon 12 --keep-going</t>
@@ -23553,7 +23265,6 @@
           <t>Retail saga</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
         <is>
           <t>v2 C=2 N=2 R=3 S=20 U=1 D=7 (hold side)</t>
@@ -23606,7 +23317,6 @@
       <c r="P329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="inlineStr"/>
       <c r="R329" t="inlineStr">
         <is>
           <t>--mode timed --variant v2 --rounds 3 --stock 20 --u 1 --deadline-ratio 7 --keep-going</t>
@@ -23619,7 +23329,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
           <t>K=2 QS=3 DD=8 U=0 H=16 (timed-only ladder top)</t>
@@ -23654,7 +23363,6 @@
       <c r="P330" t="n">
         <v>0</v>
       </c>
-      <c r="Q330" t="inlineStr"/>
       <c r="R330" t="inlineStr">
         <is>
           <t>--mode timed --ams 2 --queue-size 3 --deadline 8 --u 0 --horizon 16 --keep-going</t>
@@ -23667,7 +23375,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
           <t>K=2 QS=3 DD=8 U=0 H=14 (timed-only)</t>
@@ -23702,7 +23409,6 @@
       <c r="P331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="inlineStr"/>
       <c r="R331" t="inlineStr">
         <is>
           <t>--mode timed --ams 2 --queue-size 3 --deadline 8 --u 0 --horizon 14 --keep-going</t>
@@ -23715,7 +23421,6 @@
           <t>Retail saga</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
         <is>
           <t>v2 C=3 N=3 R=2 S=20 U=1 D=7 (paper's 3 customers)</t>
@@ -23768,7 +23473,6 @@
       <c r="P332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="inlineStr"/>
       <c r="R332" t="inlineStr">
         <is>
           <t>--mode timed --variant v2 --order-services 3 --customers 3 --rounds 2 --stock 20 --u 1 --deadline-ratio 7 --keep-going</t>
@@ -23781,7 +23485,6 @@
           <t>Retail saga</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
           <t>v2 C=2 N=2 R=4 S=20 U=1 D=7</t>
@@ -23834,7 +23537,6 @@
       <c r="P333" t="n">
         <v>0</v>
       </c>
-      <c r="Q333" t="inlineStr"/>
       <c r="R333" t="inlineStr">
         <is>
           <t>--mode timed --variant v2 --rounds 4 --stock 20 --u 1 --deadline-ratio 7 --keep-going</t>
@@ -23847,7 +23549,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr">
         <is>
           <t>K=2 QS=3 DD=7 U=0 H=8 (boundary FIRE side)</t>
@@ -23900,7 +23601,6 @@
       <c r="P334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="inlineStr"/>
       <c r="R334" t="inlineStr">
         <is>
           <t>--mode timed --ams 2 --queue-size 3 --deadline 7 --u 0 --horizon 8 --keep-going</t>
@@ -23913,7 +23613,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr">
         <is>
           <t>K=2 QS=3 DD=8 U=0 H=12</t>
@@ -23975,7 +23674,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
           <t>K=3 QS=4 DD=8 U=0 H=7</t>
@@ -24037,7 +23735,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr"/>
       <c r="C337" t="inlineStr">
         <is>
           <t>K=1 QS=2 DD=12 L=0 U=1 H=12 (transit)</t>
@@ -24090,7 +23787,6 @@
       <c r="P337" t="n">
         <v>0</v>
       </c>
-      <c r="Q337" t="inlineStr"/>
       <c r="R337" t="inlineStr">
         <is>
           <t>--mode timed --ams 1 --deadline 12 --u 1 --horizon 12 --keep-going</t>
@@ -24103,7 +23799,6 @@
           <t>Retail saga</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr">
         <is>
           <t>v2 C=2 N=2 R=3 S=20 U=1 D=6 (boundary FIRE side)</t>
@@ -24156,7 +23851,6 @@
       <c r="P338" t="n">
         <v>0</v>
       </c>
-      <c r="Q338" t="inlineStr"/>
       <c r="R338" t="inlineStr">
         <is>
           <t>--mode timed --variant v2 --rounds 3 --stock 20 --u 1 --deadline-ratio 6 --keep-going</t>
@@ -24169,7 +23863,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr"/>
       <c r="C339" t="inlineStr">
         <is>
           <t>K=1 QS=2 DD=7 U=0 H=12 (boundary FIRE side)</t>
@@ -24222,7 +23915,6 @@
       <c r="P339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="inlineStr"/>
       <c r="R339" t="inlineStr">
         <is>
           <t>--mode timed --ams 1 --deadline 7 --u 0 --horizon 12 --keep-going</t>
@@ -24235,7 +23927,6 @@
           <t>YARN scheduler</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr"/>
       <c r="C340" t="inlineStr">
         <is>
           <t>K=1 QS=2 DD=11 L=0 U=1 H=12 (U=1 boundary FIRE side)</t>
@@ -24288,7 +23979,6 @@
       <c r="P340" t="n">
         <v>0</v>
       </c>
-      <c r="Q340" t="inlineStr"/>
       <c r="R340" t="inlineStr">
         <is>
           <t>--mode timed --ams 1 --deadline 11 --u 1 --horizon 12 --keep-going</t>
@@ -24301,7 +23991,6 @@
           <t>Retail saga</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
         <is>
           <t>v1 C=2 N=2 R=2 S=20 U=1 D=9</t>
@@ -24354,7 +24043,6 @@
       <c r="P341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="inlineStr"/>
       <c r="R341" t="inlineStr">
         <is>
           <t>--mode timed --variant v1 --rounds 2 --stock 20 --u 1 --deadline-ratio 9 --keep-going</t>
@@ -24367,7 +24055,6 @@
           <t>Retail saga</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr">
         <is>
           <t>v2 C=3 N=3 R=1 S=20 U=1 D=7 (paper's 3 customers, hold side)</t>
@@ -24420,7 +24107,6 @@
       <c r="P342" t="n">
         <v>0</v>
       </c>
-      <c r="Q342" t="inlineStr"/>
       <c r="R342" t="inlineStr">
         <is>
           <t>--mode timed --variant v2 --order-services 3 --customers 3 --rounds 1 --stock 20 --u 1 --deadline-ratio 7 --keep-going</t>
@@ -24433,7 +24119,6 @@
           <t>Retail saga</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
         <is>
           <t>v2 C=3 N=3 R=1 S=20 U=1 D=6 (boundary FIRE side)</t>
@@ -24456,7 +24141,7 @@
         <v>21.6</v>
       </c>
       <c r="H343" t="n">
-        <v>17608</v>
+        <v>17544</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -24486,7 +24171,11 @@
       <c r="P343" t="n">
         <v>0</v>
       </c>
-      <c r="Q343" t="inlineStr"/>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Timed violations re-run with e96fe7a (2026-10-07): 17544 (campaign 17608 double-counted the prefix of executions whose delivered send was rejected); explored unchanged</t>
+        </is>
+      </c>
       <c r="R343" t="inlineStr">
         <is>
           <t>--mode timed --variant v2 --order-services 3 --customers 3 --rounds 1 --stock 20 --u 1 --deadline-ratio 6 --keep-going</t>
@@ -24499,7 +24188,6 @@
           <t>Comm-closed leader election</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
         <is>
           <t>N=3 B=1 regime D (l=u=20 sd=0 w=200) shared x4</t>
@@ -24546,7 +24234,6 @@
       <c r="P344" t="n">
         <v>0</v>
       </c>
-      <c r="Q344" t="inlineStr"/>
       <c r="R344" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --ballots 1 --u 20 --w 200 --l 20 --sd 0 --parallel shared</t>
@@ -24559,7 +24246,6 @@
           <t>Comm-closed leader election</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr">
         <is>
           <t>N=3 B=1 regime D (l=u=20 sd=0 w=200) 1 core</t>
@@ -24606,7 +24292,6 @@
       <c r="P345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="inlineStr"/>
       <c r="R345" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --ballots 1 --u 20 --w 200 --l 20 --sd 0 --parallel shared</t>
@@ -24619,7 +24304,6 @@
           <t>Comm-closed leader election</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
         <is>
           <t>N=3 B=1 regime A (l=18 u=20 sd=2 w=200) shared x4</t>
@@ -24666,7 +24350,6 @@
       <c r="P346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="inlineStr"/>
       <c r="R346" t="inlineStr">
         <is>
           <t>--mode timed --nodes 3 --ballots 1 --u 20 --w 200 --l 18 --sd 2 --parallel shared</t>
@@ -24679,7 +24362,6 @@
           <t>Three-phase commit</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
           <t>N=2 R=2 U=20 W/U=3 sd/U=0.25</t>
@@ -24726,7 +24408,6 @@
       <c r="P347" t="n">
         <v>0</v>
       </c>
-      <c r="Q347" t="inlineStr"/>
       <c r="R347" t="inlineStr">
         <is>
           <t>--mode timed --participants 2 --rounds 2 --u 20 --w-ratio 3 --sd-ratio 0.25</t>
@@ -24739,7 +24420,6 @@
           <t>Three-phase commit</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr">
         <is>
           <t>N=4 R=1 U=20 W/U=3 sd/U=0.25 (biggest N)</t>
@@ -24786,7 +24466,6 @@
       <c r="P348" t="n">
         <v>0</v>
       </c>
-      <c r="Q348" t="inlineStr"/>
       <c r="R348" t="inlineStr">
         <is>
           <t>--mode timed --participants 4 --rounds 1 --u 20 --w-ratio 3 --sd-ratio 0.25</t>
@@ -24799,7 +24478,6 @@
           <t>Three-phase commit</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
           <t>N=3 R=1 U=20 W/U=3 sd/U=0.25</t>
@@ -24846,7 +24524,6 @@
       <c r="P349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="inlineStr"/>
       <c r="R349" t="inlineStr">
         <is>
           <t>--mode timed --participants 3 --rounds 1 --u 20 --w-ratio 3 --sd-ratio 0.25</t>
@@ -24859,7 +24536,6 @@
           <t>Three-phase commit</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
         <is>
           <t>N=2 R=3 U=20 W/U=3 sd/U=0.25 (biggest R)</t>
@@ -24918,7 +24594,6 @@
           <t>Two-phase commit</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr">
         <is>
           <t>N=6 delta=5</t>
@@ -24965,7 +24640,6 @@
       <c r="P351" t="n">
         <v>0</v>
       </c>
-      <c r="Q351" t="inlineStr"/>
       <c r="R351" t="inlineStr">
         <is>
           <t>--mode timed --participants 6 --delta 5</t>
@@ -24978,7 +24652,6 @@
           <t>Two-phase commit</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
         <is>
           <t>N=7 delta=5 (biggest N)</t>
@@ -25025,7 +24698,6 @@
       <c r="P352" t="n">
         <v>0</v>
       </c>
-      <c r="Q352" t="inlineStr"/>
       <c r="R352" t="inlineStr">
         <is>
           <t>--mode timed --participants 7 --delta 5</t>
@@ -25038,7 +24710,6 @@
           <t>Raft leader election</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
         <is>
           <t>N=3 delta=2 (rounds is a no-op; reference only, below 10 s)</t>
@@ -25159,7 +24830,6 @@
       <c r="P354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="inlineStr"/>
       <c r="R354" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 3 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going</t>
@@ -25229,7 +24899,6 @@
       <c r="P355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="inlineStr"/>
       <c r="R355" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 3 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --keep-going</t>
@@ -25299,7 +24968,6 @@
       <c r="P356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="inlineStr"/>
       <c r="R356" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 4 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -25369,7 +25037,6 @@
       <c r="P357" t="n">
         <v>0</v>
       </c>
-      <c r="Q357" t="inlineStr"/>
       <c r="R357" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 4 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --keep-going --parallel shared</t>
@@ -25439,7 +25106,6 @@
       <c r="P358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="inlineStr"/>
       <c r="R358" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 5 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -25509,7 +25175,6 @@
       <c r="P359" t="n">
         <v>0</v>
       </c>
-      <c r="Q359" t="inlineStr"/>
       <c r="R359" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 5 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --keep-going --parallel shared</t>
@@ -25579,7 +25244,6 @@
       <c r="P360" t="n">
         <v>0</v>
       </c>
-      <c r="Q360" t="inlineStr"/>
       <c r="R360" t="inlineStr">
         <is>
           <t>--clients 3 --rounds 2 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -25649,7 +25313,6 @@
       <c r="P361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="inlineStr"/>
       <c r="R361" t="inlineStr">
         <is>
           <t>--clients 3 --rounds 2 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --keep-going --parallel shared</t>
@@ -25719,7 +25382,6 @@
       <c r="P362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="inlineStr"/>
       <c r="R362" t="inlineStr">
         <is>
           <t>--clients 2 --rounds 6 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -25852,7 +25514,6 @@
       <c r="P364" t="n">
         <v>0</v>
       </c>
-      <c r="Q364" t="inlineStr"/>
       <c r="R364" t="inlineStr">
         <is>
           <t>--clients 3 --rounds 3 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -25922,7 +25583,6 @@
       <c r="P365" t="n">
         <v>0</v>
       </c>
-      <c r="Q365" t="inlineStr"/>
       <c r="R365" t="inlineStr">
         <is>
           <t>--clients 3 --rounds 3 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing on --pause-ratio 2 --keep-going --parallel shared</t>
@@ -25992,7 +25652,6 @@
       <c r="P366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="inlineStr"/>
       <c r="R366" t="inlineStr">
         <is>
           <t>--clients 4 --rounds 2 --mode timed --u 2 --l-ratio 0 --sd-ratio 0.5 --ttl-ratio 5 --fencing off --pause-ratio 1.5 --keep-going --parallel shared</t>
@@ -26407,12 +26066,12 @@
       <c r="K14" s="6" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>finished 263 s, 1,679,317 explored, viol 63,158</t>
+          <t>finished 263 s, 1,679,317 explored, viol 48,240 (re-run e96fe7a; campaign 63,158)</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>finished 13,516 s, 69,651,425 explored, viol 2,247,921</t>
+          <t>finished 13,516 s, 69,651,425 explored, viol 1,731,960 (re-run e96fe7a; campaign 2,247,921)</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr"/>
@@ -26463,7 +26122,7 @@
       <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>finished 385 s, 1,418,181 explored, viol 55,048</t>
+          <t>finished 385 s, 1,418,181 explored, viol 41,760 (re-run e96fe7a; campaign 55,048)</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr"/>
@@ -26559,7 +26218,7 @@
       <c r="K20" s="6" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>finished 198 s, 880,309 explored, viol 50,058</t>
+          <t>finished 198 s, 880,309 explored, viol 34,416 (re-run e96fe7a; campaign 50,058)</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr"/>
@@ -26655,7 +26314,7 @@
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>finished 262 s, 1,679,317 explored, viol 63,158</t>
+          <t>finished 262 s, 1,679,317 explored, viol 48,240 (re-run e96fe7a; campaign 63,158)</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr"/>
@@ -26751,7 +26410,7 @@
       <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>finished 280 s, 711,976 explored, viol 43,100</t>
+          <t>finished 280 s, 711,976 explored, viol 29,160 (re-run e96fe7a; campaign 43,100)</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr"/>
@@ -28479,9 +28138,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
